--- a/Space Oddity/Physical Architecture interfaces.xlsx
+++ b/Space Oddity/Physical Architecture interfaces.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1c088fba97fd989/Documents/GitHub/AIAA-Systems-Engineering-Workshop/Space Oddity/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4CB6064-7F4B-4458-A1AC-C09FE3DF630D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="8_{D4CB6064-7F4B-4458-A1AC-C09FE3DF630D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E82B3A55-FE58-443C-9EED-B90BABD683E7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{6362A105-3F44-40A8-AEA1-D4C63C43300D}"/>
   </bookViews>
@@ -35,6 +35,95 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
+  <si>
+    <t>whole system</t>
+  </si>
+  <si>
+    <t>whole plane</t>
+  </si>
+  <si>
+    <t>airframe</t>
+  </si>
+  <si>
+    <t>fuselage</t>
+  </si>
+  <si>
+    <t>wings</t>
+  </si>
+  <si>
+    <t>tail</t>
+  </si>
+  <si>
+    <t>propulsion</t>
+  </si>
+  <si>
+    <t>turbine</t>
+  </si>
+  <si>
+    <t>internal ducting</t>
+  </si>
+  <si>
+    <t>control</t>
+  </si>
+  <si>
+    <t>wing control surfaces</t>
+  </si>
+  <si>
+    <t>tail control surfaces</t>
+  </si>
+  <si>
+    <t>actuating vents</t>
+  </si>
+  <si>
+    <t>computing</t>
+  </si>
+  <si>
+    <t>electrical</t>
+  </si>
+  <si>
+    <t>ground</t>
+  </si>
+  <si>
+    <t>pilot</t>
+  </si>
+  <si>
+    <t>transmitter</t>
+  </si>
+  <si>
+    <t>livemetery</t>
+  </si>
+  <si>
+    <t>1.1.1</t>
+  </si>
+  <si>
+    <t>1.1.2</t>
+  </si>
+  <si>
+    <t>1.1.3</t>
+  </si>
+  <si>
+    <t>1.2.1</t>
+  </si>
+  <si>
+    <t>1.2.2</t>
+  </si>
+  <si>
+    <t>1.3.1</t>
+  </si>
+  <si>
+    <t>1.3.2</t>
+  </si>
+  <si>
+    <t>1.3.3</t>
+  </si>
+  <si>
+    <t>2.2.1</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
@@ -46,15 +135,27 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -62,12 +163,194 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,9 +685,599 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3EEB64D-FF13-49D1-8023-0D67CF4949AA}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="A1:W21"/>
+  <sheetFormatPr defaultColWidth="7.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C1" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P1" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="R1" s="1">
+        <v>2</v>
+      </c>
+      <c r="S1" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="T1" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="2"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="10">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="2"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="2"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="2"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="2"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="2"/>
+    </row>
+    <row r="7" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="2"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="2"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="2"/>
+    </row>
+    <row r="10" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="2"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="2"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="2"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="2"/>
+    </row>
+    <row r="14" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="2"/>
+    </row>
+    <row r="15" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="2"/>
+    </row>
+    <row r="16" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+      <c r="V16" s="2"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="10">
+        <v>2</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="2"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="10">
+        <v>2.1</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+      <c r="V18" s="2"/>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="10">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="V19" s="2"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="V20" s="2"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+      <c r="W21" s="21"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Space Oddity/Physical Architecture interfaces.xlsx
+++ b/Space Oddity/Physical Architecture interfaces.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1c088fba97fd989/Documents/GitHub/AIAA-Systems-Engineering-Workshop/Space Oddity/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{D4CB6064-7F4B-4458-A1AC-C09FE3DF630D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E82B3A55-FE58-443C-9EED-B90BABD683E7}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="8_{D4CB6064-7F4B-4458-A1AC-C09FE3DF630D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{317F21E5-573B-4F13-919D-6C62669DDC7B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{6362A105-3F44-40A8-AEA1-D4C63C43300D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="33">
   <si>
     <t>whole system</t>
   </si>
@@ -120,6 +120,21 @@
   </si>
   <si>
     <t>2.2.1</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>General:</t>
+  </si>
+  <si>
+    <t>Mechanical Interface:</t>
+  </si>
+  <si>
+    <t>"There in an interface from [left] to [top]."</t>
+  </si>
+  <si>
+    <t>"[left] is mounted to [top]."</t>
   </si>
 </sst>
 </file>
@@ -292,65 +307,50 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -366,6 +366,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -685,596 +689,740 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3EEB64D-FF13-49D1-8023-0D67CF4949AA}">
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr defaultColWidth="7.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="C1" s="1">
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1">
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="1">
+      <c r="I2" s="1">
         <v>1.2</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="1">
+      <c r="L2" s="1">
         <v>1.3</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="P1" s="1">
+      <c r="P2" s="1">
         <v>1.4</v>
       </c>
-      <c r="Q1" s="1">
+      <c r="Q2" s="1">
         <v>1.5</v>
       </c>
-      <c r="R1" s="1">
+      <c r="R2" s="1">
         <v>2</v>
       </c>
-      <c r="S1" s="1">
+      <c r="S2" s="1">
         <v>2.1</v>
       </c>
-      <c r="T1" s="1">
+      <c r="T2" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="V1" s="2"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="V2" s="2"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B3" s="1">
         <v>0</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="2"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="2"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B4" s="1">
         <v>1</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="2"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="2"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B5" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="2"/>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="11"/>
+      <c r="H5" s="4"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="11"/>
+      <c r="K5" s="4"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="16"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="5"/>
       <c r="Q5" s="1"/>
-      <c r="R5" s="4"/>
+      <c r="R5" s="3"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
       <c r="V5" s="2"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="11"/>
+      <c r="G6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>28</v>
+      </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="11"/>
+      <c r="J6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>28</v>
+      </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="4"/>
+      <c r="O6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="R6" s="3"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
       <c r="V6" s="2"/>
     </row>
-    <row r="7" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="17"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="4"/>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N7" s="1"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="R7" s="3"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
       <c r="V7" s="2"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="10">
-        <v>1.2</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
+    <row r="8" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
-      <c r="H8" s="13"/>
+      <c r="H8" s="7"/>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
-      <c r="K8" s="13"/>
+      <c r="K8" s="7"/>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="18"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="4"/>
+      <c r="N8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="O8" s="7"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R8" s="3"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
       <c r="V8" s="2"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="4"/>
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="3"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
       <c r="V9" s="2"/>
     </row>
-    <row r="10" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="19"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="4"/>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="R10" s="3"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
       <c r="V10" s="2"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="10">
-        <v>1.3</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
+    <row r="11" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
-      <c r="H11" s="13"/>
+      <c r="H11" s="7"/>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
-      <c r="K11" s="13"/>
+      <c r="K11" s="7"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="18"/>
+      <c r="O11" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P11" s="8"/>
       <c r="Q11" s="6"/>
-      <c r="R11" s="4"/>
+      <c r="R11" s="3"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
       <c r="V11" s="2"/>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="7"/>
-      <c r="R12" s="4"/>
+      <c r="A12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="3"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
       <c r="V12" s="2"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="4"/>
+      <c r="A13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="R13" s="3"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
       <c r="V13" s="2"/>
     </row>
-    <row r="14" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="19"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="4"/>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="R14" s="3"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
       <c r="V14" s="2"/>
     </row>
     <row r="15" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="10">
-        <v>1.4</v>
-      </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="20"/>
-      <c r="Q15" s="9"/>
-      <c r="R15" s="4"/>
+      <c r="A15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R15" s="3"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
       <c r="V15" s="2"/>
     </row>
     <row r="16" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="4"/>
+      <c r="A16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="13"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="R16" s="3"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
       <c r="V16" s="2"/>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row r="17" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="3"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+      <c r="V17" s="2"/>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B18" s="1">
         <v>2</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
-      <c r="V17" s="2"/>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+      <c r="U18" s="3"/>
+      <c r="V18" s="2"/>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B19" s="1">
         <v>2.1</v>
-      </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="4"/>
-      <c r="S18" s="1"/>
-      <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="2"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="10">
-        <v>2.2000000000000002</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
       <c r="R19" s="3"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
       <c r="V19" s="2"/>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>27</v>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="1">
+        <v>2.2000000000000002</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
       <c r="R20" s="3"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
       <c r="V20" s="2"/>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="3"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
       <c r="V21" s="2"/>
-      <c r="W21" s="21"/>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
